--- a/lai/valuationquan/AILOF/csiAILOFmodel4meancn.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4meancn.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="37">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -153,6 +153,18 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>均线</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能产业LOF</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>SMA之MAX</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -169,6 +181,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>RSV</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -183,10 +199,6 @@
   <si>
     <t>J</t>
     <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>均线</t>
@@ -887,7 +899,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1220,6 +1232,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1229,7 +1244,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1561,6 +1576,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1604,7 +1622,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1937,6 +1955,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1946,7 +1967,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2278,6 +2299,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2321,7 +2345,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2654,6 +2678,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2663,7 +2690,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2995,6 +3022,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -3017,11 +3047,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="504617984"/>
-        <c:axId val="504632832"/>
+        <c:axId val="591581952"/>
+        <c:axId val="591583488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="504617984"/>
+        <c:axId val="591581952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3064,14 +3094,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="504632832"/>
+        <c:crossAx val="591583488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="504632832"/>
+        <c:axId val="591583488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3120,7 +3150,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="504617984"/>
+        <c:crossAx val="591581952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3334,7 +3364,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3667,6 +3697,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3676,7 +3709,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4008,6 +4041,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -4051,7 +4087,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4384,6 +4420,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4393,7 +4432,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4725,6 +4764,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4768,7 +4810,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5101,6 +5143,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5110,7 +5155,7 @@
               <c:f>'模型四 (1)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5442,6 +5487,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5464,11 +5512,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="521819264"/>
-        <c:axId val="521820800"/>
+        <c:axId val="592043008"/>
+        <c:axId val="592201984"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="521819264"/>
+        <c:axId val="592043008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5511,14 +5559,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521820800"/>
+        <c:crossAx val="592201984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="521820800"/>
+        <c:axId val="592201984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5567,7 +5615,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521819264"/>
+        <c:crossAx val="592043008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5781,7 +5829,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6114,6 +6162,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6123,7 +6174,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6455,6 +6506,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6498,7 +6552,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6831,6 +6885,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6840,7 +6897,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7172,6 +7229,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -7215,7 +7275,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7548,6 +7608,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7557,7 +7620,7 @@
               <c:f>'模型四 (1)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7889,6 +7952,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7911,11 +7977,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529965056"/>
-        <c:axId val="529966976"/>
+        <c:axId val="671334400"/>
+        <c:axId val="671336320"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529965056"/>
+        <c:axId val="671334400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7958,14 +8024,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529966976"/>
+        <c:crossAx val="671336320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529966976"/>
+        <c:axId val="671336320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8014,7 +8080,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529965056"/>
+        <c:crossAx val="671334400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8228,7 +8294,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8561,6 +8627,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8570,7 +8639,7 @@
               <c:f>'模型四 (1)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8902,6 +8971,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8945,7 +9017,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9278,6 +9350,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9287,7 +9362,7 @@
               <c:f>'模型四 (1)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9619,6 +9694,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9662,7 +9740,7 @@
               <c:f>'模型四 (1)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9995,6 +10073,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10004,7 +10085,7 @@
               <c:f>'模型四 (1)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10336,6 +10417,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -10358,11 +10442,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="577520768"/>
-        <c:axId val="577522304"/>
+        <c:axId val="732011136"/>
+        <c:axId val="732025216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="577520768"/>
+        <c:axId val="732011136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10405,14 +10489,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577522304"/>
+        <c:crossAx val="732025216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="577522304"/>
+        <c:axId val="732025216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10461,7 +10545,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577520768"/>
+        <c:crossAx val="732011136"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10675,7 +10759,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11008,6 +11092,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11017,7 +11104,7 @@
               <c:f>'模型四 (3)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11349,6 +11436,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -11392,7 +11482,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11725,6 +11815,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11734,7 +11827,7 @@
               <c:f>'模型四 (3)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12066,6 +12159,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -12109,7 +12205,7 @@
               <c:f>'模型四 (3)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12442,6 +12538,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12451,7 +12550,7 @@
               <c:f>'模型四 (3)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12783,6 +12882,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12805,11 +12907,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="577619840"/>
-        <c:axId val="577621376"/>
+        <c:axId val="732137344"/>
+        <c:axId val="732148480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="577619840"/>
+        <c:axId val="732137344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12852,14 +12954,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577621376"/>
+        <c:crossAx val="732148480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="577621376"/>
+        <c:axId val="732148480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12908,7 +13010,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577619840"/>
+        <c:crossAx val="732137344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13122,7 +13224,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13455,6 +13557,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13464,7 +13569,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13796,6 +13901,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13839,7 +13947,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14172,6 +14280,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14181,7 +14292,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14513,6 +14624,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -14556,7 +14670,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14889,6 +15003,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14898,7 +15015,7 @@
               <c:f>'模型四 (3)平均线计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15230,6 +15347,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -15252,11 +15372,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="577676800"/>
-        <c:axId val="577678336"/>
+        <c:axId val="734975488"/>
+        <c:axId val="734987008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="577676800"/>
+        <c:axId val="734975488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15299,14 +15419,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577678336"/>
+        <c:crossAx val="734987008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="577678336"/>
+        <c:axId val="734987008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15355,7 +15475,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577676800"/>
+        <c:crossAx val="734975488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15569,7 +15689,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15902,6 +16022,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15911,7 +16034,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16243,6 +16366,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -16286,7 +16412,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16619,6 +16745,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16628,7 +16757,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16960,6 +17089,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -17003,7 +17135,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17336,6 +17468,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17345,7 +17480,7 @@
               <c:f>'模型四 (3)平均线计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17677,6 +17812,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -17699,11 +17837,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="578388736"/>
-        <c:axId val="578390272"/>
+        <c:axId val="569135872"/>
+        <c:axId val="569137408"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="578388736"/>
+        <c:axId val="569135872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17746,14 +17884,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578390272"/>
+        <c:crossAx val="569137408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="578390272"/>
+        <c:axId val="569137408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17802,7 +17940,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578388736"/>
+        <c:crossAx val="569135872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18016,7 +18154,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18349,6 +18487,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18358,7 +18499,7 @@
               <c:f>'模型四 (3)平均线成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18690,6 +18831,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -18733,7 +18877,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -19066,6 +19210,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19075,7 +19222,7 @@
               <c:f>'模型四 (3)平均线成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19407,6 +19554,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -19450,7 +19600,7 @@
               <c:f>'模型四 (3)平均线成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -19783,6 +19933,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19792,7 +19945,7 @@
               <c:f>'模型四 (3)平均线成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -20124,6 +20277,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -20146,11 +20302,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="486861056"/>
-        <c:axId val="487063552"/>
+        <c:axId val="569165696"/>
+        <c:axId val="569167232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="486861056"/>
+        <c:axId val="569165696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20193,14 +20349,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487063552"/>
+        <c:crossAx val="569167232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="487063552"/>
+        <c:axId val="569167232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20249,7 +20405,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="486861056"/>
+        <c:crossAx val="569165696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20971,7 +21127,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF114"/>
+  <dimension ref="A1:AF115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25654,6 +25810,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="115" spans="1:11" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I115" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J115" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K115" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -25672,7 +25863,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25707,10 +25898,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>2</v>
@@ -25740,16 +25931,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -31683,16 +31874,63 @@
         <v>1938.211964032281</v>
       </c>
       <c r="L114" s="26">
-        <v>0.19018078074406178</v>
+        <v>0.22298399794060811</v>
       </c>
       <c r="M114" s="27">
-        <v>0.25423220629573501</v>
+        <v>0.27636018590033579</v>
       </c>
       <c r="N114" s="27">
-        <v>74.805935689687729</v>
+        <v>80.686006638099158</v>
       </c>
       <c r="O114" s="27">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I115" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J115" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K115" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L115" s="26">
+        <v>0.1858199982838401</v>
+      </c>
+      <c r="M115" s="27">
+        <v>0.33763349715124008</v>
+      </c>
+      <c r="N115" s="27">
+        <v>55.036007935137903</v>
+      </c>
+      <c r="O115" s="27">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -31713,7 +31951,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31748,13 +31986,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -31781,19 +32019,19 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>28</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -31818,7 +32056,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -38015,18 +38253,68 @@
         <v>1152.2841821809159</v>
       </c>
       <c r="L114" s="26">
-        <v>86.321154877675269</v>
+        <v>99.924817475329945</v>
       </c>
       <c r="M114" s="27">
-        <v>81.396334035405502</v>
+        <v>87.572495182046978</v>
       </c>
       <c r="N114" s="27">
-        <v>77.031747408613512</v>
+        <v>80.545329999757996</v>
       </c>
       <c r="O114" s="27">
-        <v>90.125507288989468</v>
+        <v>101.62682554662496</v>
       </c>
       <c r="P114" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I115" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J115" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K115" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L115" s="26">
+        <v>48.239429998294135</v>
+      </c>
+      <c r="M115" s="27">
+        <v>74.461473454129361</v>
+      </c>
+      <c r="N115" s="27">
+        <v>78.51737781788178</v>
+      </c>
+      <c r="O115" s="27">
+        <v>66.349664726624525</v>
+      </c>
+      <c r="P115" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -38048,7 +38336,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -38088,19 +38376,19 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>3</v>
@@ -43409,6 +43697,47 @@
         <v>212.99681655802686</v>
       </c>
       <c r="M114" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="20">
+        <v>842345</v>
+      </c>
+      <c r="E115" s="20">
+        <v>1833164.83510292</v>
+      </c>
+      <c r="F115" s="21">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>0</v>
+      </c>
+      <c r="I115" s="22">
+        <v>0</v>
+      </c>
+      <c r="J115" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K115" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L115" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M115" s="21">
         <v>579.4237932103814</v>
       </c>
     </row>
@@ -43430,7 +43759,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF114"/>
+  <dimension ref="A1:AF115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -43471,7 +43800,7 @@
         <v>21</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -48110,6 +48439,41 @@
         <v>105.19592685297673</v>
       </c>
       <c r="K114" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I115" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J115" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K115" s="21">
         <v>260.7091440429981</v>
       </c>
     </row>
@@ -48131,7 +48495,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -48166,13 +48530,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -48199,16 +48563,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -48233,7 +48597,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -54142,16 +54506,63 @@
         <v>425.75844436164391</v>
       </c>
       <c r="L114" s="26">
-        <v>0.19018078074406178</v>
+        <v>0.22298399794060811</v>
       </c>
       <c r="M114" s="27">
-        <v>0.25423220629573501</v>
+        <v>0.27636018590033579</v>
       </c>
       <c r="N114" s="27">
-        <v>74.805935689687729</v>
+        <v>80.686006638099158</v>
       </c>
       <c r="O114" s="27">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="21">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I115" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J115" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K115" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L115" s="26">
+        <v>0.1858199982838401</v>
+      </c>
+      <c r="M115" s="27">
+        <v>0.33763349715124008</v>
+      </c>
+      <c r="N115" s="27">
+        <v>55.036007935137903</v>
+      </c>
+      <c r="O115" s="27">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -54172,7 +54583,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -54207,13 +54618,13 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>3</v>
@@ -54240,19 +54651,19 @@
         <v>10</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="14" t="s">
         <v>28</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="18" customFormat="1" ht="15" customHeight="1">
@@ -60473,18 +60884,68 @@
         <v>242.17499191669597</v>
       </c>
       <c r="L114" s="26">
-        <v>86.321154877675269</v>
+        <v>99.924817475329945</v>
       </c>
       <c r="M114" s="27">
-        <v>81.396334035405502</v>
+        <v>87.572495182046978</v>
       </c>
       <c r="N114" s="27">
-        <v>77.031747408613512</v>
+        <v>80.545329999757996</v>
       </c>
       <c r="O114" s="27">
-        <v>90.125507288989468</v>
+        <v>101.62682554662496</v>
       </c>
       <c r="P114" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I115" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J115" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K115" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L115" s="26">
+        <v>48.239429998294135</v>
+      </c>
+      <c r="M115" s="27">
+        <v>74.461473454129361</v>
+      </c>
+      <c r="N115" s="27">
+        <v>78.51737781788178</v>
+      </c>
+      <c r="O115" s="27">
+        <v>66.349664726624525</v>
+      </c>
+      <c r="P115" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -60506,7 +60967,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -60546,19 +61007,19 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="30" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>3</v>
@@ -65870,6 +66331,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="115" spans="1:13" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="20">
+        <v>842345</v>
+      </c>
+      <c r="E115" s="20">
+        <v>1833164.83510292</v>
+      </c>
+      <c r="F115" s="21">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>0</v>
+      </c>
+      <c r="I115" s="22">
+        <v>0</v>
+      </c>
+      <c r="J115" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K115" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L115" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M115" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
